--- a/feedback_forms/018_team_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/018_team_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat disagree'}</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Somewhat agree'}</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'team_members_often_work_together_on_tasks_and_projects'}</t>
+          <t>team_members_often_work_together_on_tasks_and_projects</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Team members often work together on tasks and projects'}</t>
+          <t>Team members often work together on tasks and projects</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'team_members_often_share_knowledge_and_ideas'}</t>
+          <t>team_members_often_share_knowledge_and_ideas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Team members often share knowledge and ideas'}</t>
+          <t>Team members often share knowledge and ideas</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'team_members_often_help_each_other_with_work'}</t>
+          <t>team_members_often_help_each_other_with_work</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Team members often help each other with work'}</t>
+          <t>Team members often help each other with work</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'team_members_often_communicate_effectively'}</t>
+          <t>team_members_often_communicate_effectively</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Team members often communicate effectively'}</t>
+          <t>Team members often communicate effectively</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'top-down'}</t>
+          <t>top-down</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Top-down'}</t>
+          <t>Top-down</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'bottom-up'}</t>
+          <t>bottom-up</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Bottom-up'}</t>
+          <t>Bottom-up</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'not_often'}</t>
+          <t>not_often</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Not often'}</t>
+          <t>Not often</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Almost always'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'instant_messenger'}</t>
+          <t>instant_messenger</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Instant Messenger'}</t>
+          <t>Instant Messenger</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'asana'}</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Asana'}</t>
+          <t>Asana</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'trello'}</t>
+          <t>trello</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Trello'}</t>
+          <t>Trello</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'slack'}</t>
+          <t>slack</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Slack'}</t>
+          <t>Slack</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'microsoft_teams'}</t>
+          <t>microsoft_teams</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Microsoft Teams'}</t>
+          <t>Microsoft Teams</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'less_than_20'}</t>
+          <t>less_than_20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Less than 20'}</t>
+          <t>Less than 20</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'21-40'}</t>
+          <t>21-40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '21-40'}</t>
+          <t>21-40</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'41-60'}</t>
+          <t>41-60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '41-60'}</t>
+          <t>41-60</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'61-80'}</t>
+          <t>61-80</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '61-80'}</t>
+          <t>61-80</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'81-100'}</t>
+          <t>81-100</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '81-100'}</t>
+          <t>81-100</t>
         </is>
       </c>
     </row>
